--- a/src/main/resources/espacios/0 Step/0 - A1.xlsx
+++ b/src/main/resources/espacios/0 Step/0 - A1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="2 A1" sheetId="1" state="visible" r:id="rId3"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2345" uniqueCount="1733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2460" uniqueCount="1733">
   <si>
     <t xml:space="preserve">Bend your left elbow.</t>
   </si>
@@ -5234,7 +5234,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -5255,6 +5255,11 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -5305,7 +5310,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5315,6 +5320,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9318,9 +9327,6 @@
       <c r="D20" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
@@ -9416,6 +9422,9 @@
       <c r="D27" s="1" t="s">
         <v>802</v>
       </c>
+      <c r="F27" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
@@ -9455,6 +9464,9 @@
       <c r="D30" s="1" t="s">
         <v>811</v>
       </c>
+      <c r="F30" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
@@ -9494,6 +9506,9 @@
       <c r="D33" s="1" t="s">
         <v>820</v>
       </c>
+      <c r="F33" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
@@ -9519,6 +9534,9 @@
       <c r="D35" s="1" t="s">
         <v>826</v>
       </c>
+      <c r="F35" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
@@ -9544,6 +9562,9 @@
       <c r="D37" s="1" t="s">
         <v>832</v>
       </c>
+      <c r="F37" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
@@ -9569,6 +9590,9 @@
       <c r="D39" s="1" t="s">
         <v>838</v>
       </c>
+      <c r="F39" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
@@ -9580,9 +9604,6 @@
       <c r="D40" s="1" t="s">
         <v>841</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
@@ -9594,6 +9615,9 @@
       <c r="D41" s="1" t="s">
         <v>844</v>
       </c>
+      <c r="F41" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
@@ -9619,6 +9643,9 @@
       <c r="D43" s="1" t="s">
         <v>850</v>
       </c>
+      <c r="F43" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
@@ -9643,6 +9670,9 @@
       </c>
       <c r="D45" s="1" t="s">
         <v>856</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9945,6 +9975,9 @@
       <c r="D7" s="1" t="s">
         <v>916</v>
       </c>
+      <c r="F7" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
@@ -10026,6 +10059,9 @@
       <c r="D13" s="1" t="s">
         <v>934</v>
       </c>
+      <c r="F13" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
@@ -10188,6 +10224,9 @@
       <c r="D25" s="1" t="s">
         <v>970</v>
       </c>
+      <c r="F25" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
@@ -10269,6 +10308,9 @@
       <c r="D31" s="1" t="s">
         <v>988</v>
       </c>
+      <c r="F31" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
@@ -10431,6 +10473,9 @@
       <c r="D43" s="1" t="s">
         <v>1023</v>
       </c>
+      <c r="F43" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
@@ -10512,6 +10557,9 @@
       <c r="D49" s="1" t="s">
         <v>1041</v>
       </c>
+      <c r="F49" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
@@ -10674,6 +10722,9 @@
       <c r="D61" s="1" t="s">
         <v>1076</v>
       </c>
+      <c r="F61" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
@@ -10755,6 +10806,9 @@
       <c r="D67" s="1" t="s">
         <v>1094</v>
       </c>
+      <c r="F67" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
@@ -10917,6 +10971,9 @@
       <c r="D79" s="1" t="s">
         <v>1128</v>
       </c>
+      <c r="F79" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
@@ -10998,6 +11055,9 @@
       <c r="D85" s="1" t="s">
         <v>1146</v>
       </c>
+      <c r="F85" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
@@ -11160,6 +11220,9 @@
       <c r="D97" s="1" t="s">
         <v>1181</v>
       </c>
+      <c r="F97" s="3" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
@@ -11241,6 +11304,9 @@
       <c r="D103" s="1" t="s">
         <v>1199</v>
       </c>
+      <c r="F103" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
@@ -11403,6 +11469,9 @@
       <c r="D115" s="1" t="s">
         <v>1234</v>
       </c>
+      <c r="F115" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
@@ -11484,6 +11553,9 @@
       <c r="D121" s="1" t="s">
         <v>1251</v>
       </c>
+      <c r="F121" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
@@ -11646,6 +11718,9 @@
       <c r="D133" s="1" t="s">
         <v>1287</v>
       </c>
+      <c r="F133" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
@@ -11727,6 +11802,9 @@
       <c r="D139" s="1" t="s">
         <v>1305</v>
       </c>
+      <c r="F139" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="s">
@@ -11889,6 +11967,9 @@
       <c r="D151" s="1" t="s">
         <v>1340</v>
       </c>
+      <c r="F151" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="s">
@@ -11969,6 +12050,9 @@
       </c>
       <c r="D157" s="1" t="s">
         <v>1357</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12158,6 +12242,9 @@
       <c r="D7" s="1" t="s">
         <v>1393</v>
       </c>
+      <c r="F7" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
@@ -12239,6 +12326,9 @@
       <c r="D13" s="1" t="s">
         <v>1411</v>
       </c>
+      <c r="F13" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
@@ -12401,6 +12491,9 @@
       <c r="D25" s="1" t="s">
         <v>1447</v>
       </c>
+      <c r="F25" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
@@ -12482,6 +12575,9 @@
       <c r="D31" s="1" t="s">
         <v>1465</v>
       </c>
+      <c r="F31" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
@@ -12644,6 +12740,9 @@
       <c r="D43" s="1" t="s">
         <v>1501</v>
       </c>
+      <c r="F43" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
@@ -12725,6 +12824,9 @@
       <c r="D49" s="1" t="s">
         <v>1519</v>
       </c>
+      <c r="F49" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
@@ -12887,6 +12989,9 @@
       <c r="D61" s="1" t="s">
         <v>1555</v>
       </c>
+      <c r="F61" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
@@ -12968,6 +13073,9 @@
       <c r="D67" s="1" t="s">
         <v>1573</v>
       </c>
+      <c r="F67" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
@@ -13130,6 +13238,9 @@
       <c r="D79" s="1" t="s">
         <v>1609</v>
       </c>
+      <c r="F79" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
@@ -13211,6 +13322,9 @@
       <c r="D85" s="1" t="s">
         <v>1627</v>
       </c>
+      <c r="F85" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
@@ -13373,6 +13487,9 @@
       <c r="D97" s="1" t="s">
         <v>1663</v>
       </c>
+      <c r="F97" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
@@ -13454,6 +13571,9 @@
       <c r="D103" s="1" t="s">
         <v>1681</v>
       </c>
+      <c r="F103" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
@@ -13615,6 +13735,9 @@
       </c>
       <c r="D115" s="1" t="s">
         <v>1717</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13703,210 +13826,442 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A40"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="37.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="37.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="41.08"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="B2" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="B3" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="B4" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="B5" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="B6" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="B7" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="B8" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="B9" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="B10" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="B11" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
         <v>34</v>
       </c>
+      <c r="B12" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
         <v>37</v>
       </c>
+      <c r="B13" s="0" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="B14" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="B15" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
         <v>46</v>
       </c>
+      <c r="B16" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
         <v>49</v>
       </c>
+      <c r="B17" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
         <v>52</v>
       </c>
+      <c r="B18" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
         <v>55</v>
       </c>
+      <c r="B19" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="B20" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="F20" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
         <v>61</v>
       </c>
+      <c r="B21" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
         <v>64</v>
       </c>
+      <c r="B22" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="F22" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
         <v>67</v>
       </c>
+      <c r="B23" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="F23" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
         <v>70</v>
       </c>
+      <c r="B24" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="F24" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
         <v>73</v>
       </c>
+      <c r="B25" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="F25" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
         <v>76</v>
       </c>
+      <c r="B26" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="F26" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
         <v>79</v>
       </c>
+      <c r="B27" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F27" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
         <v>82</v>
       </c>
+      <c r="B28" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="F28" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
         <v>85</v>
       </c>
+      <c r="B29" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="F29" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
         <v>88</v>
       </c>
+      <c r="B30" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="F30" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
         <v>91</v>
       </c>
+      <c r="B31" s="0" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
         <v>91</v>
       </c>
+      <c r="B32" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="F32" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
         <v>94</v>
       </c>
+      <c r="B33" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="F33" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
         <v>94</v>
       </c>
+      <c r="B34" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="F34" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
         <v>97</v>
       </c>
+      <c r="B35" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="F35" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
         <v>100</v>
       </c>
+      <c r="B36" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="F36" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
         <v>103</v>
       </c>
+      <c r="B37" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="F37" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
         <v>106</v>
       </c>
+      <c r="B38" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="F38" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
         <v>109</v>
       </c>
+      <c r="B39" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="F39" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
         <v>112</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="F40" s="0" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/espacios/0 Step/0 - A1.xlsx
+++ b/src/main/resources/espacios/0 Step/0 - A1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="2 A1" sheetId="1" state="visible" r:id="rId3"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2460" uniqueCount="1733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2484" uniqueCount="1734">
   <si>
     <t xml:space="preserve">Bend your left elbow.</t>
   </si>
@@ -2732,6 +2732,9 @@
   </si>
   <si>
     <t xml:space="preserve">aɪ ˈɔlˌmoʊst fərˈɡɑt jʊər bʊk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEAD</t>
   </si>
   <si>
     <t xml:space="preserve">She's almost done with the project.</t>
@@ -5234,7 +5237,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -5255,11 +5258,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -5310,7 +5308,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5320,10 +5318,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5735,6 +5729,9 @@
       <c r="D20" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="F20" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
@@ -6289,6 +6286,9 @@
       <c r="D60" s="1" t="s">
         <v>174</v>
       </c>
+      <c r="F60" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
@@ -6843,6 +6843,9 @@
       <c r="D100" s="1" t="s">
         <v>288</v>
       </c>
+      <c r="F100" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
@@ -7119,6 +7122,9 @@
       </c>
       <c r="D120" s="1" t="s">
         <v>348</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7560,6 +7566,9 @@
       <c r="D20" s="1" t="s">
         <v>426</v>
       </c>
+      <c r="F20" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
@@ -8100,6 +8109,9 @@
       <c r="D59" s="1" t="s">
         <v>529</v>
       </c>
+      <c r="F59" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
@@ -8362,6 +8374,9 @@
       </c>
       <c r="D78" s="1" t="s">
         <v>583</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8845,6 +8860,9 @@
       <c r="D14" s="1" t="s">
         <v>682</v>
       </c>
+      <c r="F14" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
@@ -9327,6 +9345,9 @@
       <c r="D20" s="1" t="s">
         <v>781</v>
       </c>
+      <c r="F20" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
@@ -9603,6 +9624,9 @@
       </c>
       <c r="D40" s="1" t="s">
         <v>841</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9906,18 +9930,18 @@
         <v>901</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>6</v>
@@ -9925,13 +9949,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>6</v>
@@ -9939,13 +9963,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>6</v>
@@ -9953,13 +9977,13 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>6</v>
@@ -9967,27 +9991,27 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>6</v>
@@ -9995,13 +10019,13 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>6</v>
@@ -10009,13 +10033,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>6</v>
@@ -10023,13 +10047,13 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>6</v>
@@ -10037,13 +10061,13 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>6</v>
@@ -10051,27 +10075,27 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>6</v>
@@ -10079,13 +10103,13 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>6</v>
@@ -10093,13 +10117,13 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>6</v>
@@ -10107,13 +10131,13 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>6</v>
@@ -10121,13 +10145,13 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>6</v>
@@ -10135,24 +10159,27 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>952</v>
+        <v>953</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>6</v>
@@ -10160,13 +10187,13 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>6</v>
@@ -10174,13 +10201,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>6</v>
@@ -10188,13 +10215,13 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>6</v>
@@ -10202,13 +10229,13 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>6</v>
@@ -10216,27 +10243,27 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>6</v>
@@ -10244,13 +10271,13 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>6</v>
@@ -10258,13 +10285,13 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>6</v>
@@ -10272,13 +10299,13 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>6</v>
@@ -10286,13 +10313,13 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>6</v>
@@ -10300,27 +10327,27 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>6</v>
@@ -10328,13 +10355,13 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>6</v>
@@ -10342,13 +10369,13 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>6</v>
@@ -10356,13 +10383,13 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>6</v>
@@ -10370,13 +10397,13 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>6</v>
@@ -10384,24 +10411,27 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>1005</v>
+        <v>1006</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>6</v>
@@ -10409,13 +10439,13 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>6</v>
@@ -10423,13 +10453,13 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>6</v>
@@ -10437,13 +10467,13 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>6</v>
@@ -10451,13 +10481,13 @@
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>6</v>
@@ -10465,27 +10495,27 @@
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>6</v>
@@ -10493,13 +10523,13 @@
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>6</v>
@@ -10507,13 +10537,13 @@
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>6</v>
@@ -10521,13 +10551,13 @@
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>6</v>
@@ -10535,13 +10565,13 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>6</v>
@@ -10549,27 +10579,27 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>6</v>
@@ -10577,13 +10607,13 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>6</v>
@@ -10591,13 +10621,13 @@
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>6</v>
@@ -10605,13 +10635,13 @@
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>6</v>
@@ -10619,13 +10649,13 @@
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>6</v>
@@ -10633,24 +10663,27 @@
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>1058</v>
+        <v>1059</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>6</v>
@@ -10658,13 +10691,13 @@
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>6</v>
@@ -10672,13 +10705,13 @@
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>6</v>
@@ -10686,13 +10719,13 @@
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>6</v>
@@ -10700,13 +10733,13 @@
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>6</v>
@@ -10714,27 +10747,27 @@
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>6</v>
@@ -10742,13 +10775,13 @@
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>6</v>
@@ -10756,13 +10789,13 @@
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>6</v>
@@ -10770,13 +10803,13 @@
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>6</v>
@@ -10784,13 +10817,13 @@
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>6</v>
@@ -10798,27 +10831,27 @@
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>6</v>
@@ -10826,13 +10859,13 @@
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>6</v>
@@ -10840,13 +10873,13 @@
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>6</v>
@@ -10854,13 +10887,13 @@
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>6</v>
@@ -10868,13 +10901,13 @@
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>6</v>
@@ -10882,24 +10915,27 @@
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>1111</v>
+        <v>1112</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>6</v>
@@ -10907,13 +10943,13 @@
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>6</v>
@@ -10921,13 +10957,13 @@
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>6</v>
@@ -10935,13 +10971,13 @@
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>6</v>
@@ -10949,13 +10985,13 @@
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>6</v>
@@ -10963,27 +10999,27 @@
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>897</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>6</v>
@@ -10991,13 +11027,13 @@
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>6</v>
@@ -11005,13 +11041,13 @@
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>6</v>
@@ -11019,13 +11055,13 @@
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>6</v>
@@ -11033,13 +11069,13 @@
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>6</v>
@@ -11047,27 +11083,27 @@
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>6</v>
@@ -11075,13 +11111,13 @@
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>6</v>
@@ -11089,13 +11125,13 @@
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>6</v>
@@ -11103,13 +11139,13 @@
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>6</v>
@@ -11117,13 +11153,13 @@
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>6</v>
@@ -11131,24 +11167,27 @@
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>1164</v>
+        <v>1165</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>6</v>
@@ -11156,13 +11195,13 @@
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>6</v>
@@ -11170,13 +11209,13 @@
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>6</v>
@@ -11184,13 +11223,13 @@
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>6</v>
@@ -11198,13 +11237,13 @@
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>6</v>
@@ -11212,27 +11251,27 @@
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>1181</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>6</v>
+        <v>1182</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>6</v>
@@ -11240,13 +11279,13 @@
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>6</v>
@@ -11254,13 +11293,13 @@
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>6</v>
@@ -11268,13 +11307,13 @@
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>6</v>
@@ -11282,13 +11321,13 @@
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>6</v>
@@ -11296,27 +11335,27 @@
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>6</v>
@@ -11324,13 +11363,13 @@
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>6</v>
@@ -11338,13 +11377,13 @@
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>6</v>
@@ -11352,13 +11391,13 @@
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>6</v>
@@ -11366,13 +11405,13 @@
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>6</v>
@@ -11380,24 +11419,27 @@
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>1217</v>
+        <v>1218</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>6</v>
@@ -11405,13 +11447,13 @@
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>6</v>
@@ -11419,13 +11461,13 @@
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>6</v>
@@ -11433,13 +11475,13 @@
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>6</v>
@@ -11447,13 +11489,13 @@
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>6</v>
@@ -11461,27 +11503,27 @@
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>6</v>
@@ -11489,13 +11531,13 @@
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>6</v>
@@ -11503,13 +11545,13 @@
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>6</v>
@@ -11517,13 +11559,13 @@
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>6</v>
@@ -11531,13 +11573,13 @@
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>6</v>
@@ -11545,27 +11587,27 @@
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>6</v>
@@ -11573,13 +11615,13 @@
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>6</v>
@@ -11587,13 +11629,13 @@
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>6</v>
@@ -11601,13 +11643,13 @@
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>6</v>
@@ -11615,13 +11657,13 @@
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>6</v>
@@ -11629,24 +11671,27 @@
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>1269</v>
+        <v>1270</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>6</v>
@@ -11654,13 +11699,13 @@
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>6</v>
@@ -11668,13 +11713,13 @@
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>6</v>
@@ -11682,13 +11727,13 @@
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>6</v>
@@ -11696,13 +11741,13 @@
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>6</v>
@@ -11710,27 +11755,27 @@
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>6</v>
@@ -11738,13 +11783,13 @@
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>6</v>
@@ -11752,13 +11797,13 @@
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>6</v>
@@ -11766,13 +11811,13 @@
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>6</v>
@@ -11780,13 +11825,13 @@
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>6</v>
@@ -11794,27 +11839,27 @@
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>6</v>
@@ -11822,13 +11867,13 @@
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>6</v>
@@ -11836,13 +11881,13 @@
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>6</v>
@@ -11850,13 +11895,13 @@
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>6</v>
@@ -11864,13 +11909,13 @@
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>6</v>
@@ -11878,24 +11923,27 @@
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>1323</v>
+        <v>1324</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>6</v>
@@ -11903,13 +11951,13 @@
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>6</v>
@@ -11917,13 +11965,13 @@
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>6</v>
@@ -11931,13 +11979,13 @@
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>6</v>
@@ -11945,13 +11993,13 @@
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>6</v>
@@ -11959,27 +12007,27 @@
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>6</v>
@@ -11987,13 +12035,13 @@
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>6</v>
@@ -12001,13 +12049,13 @@
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>6</v>
@@ -12015,13 +12063,13 @@
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>6</v>
@@ -12029,13 +12077,13 @@
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>6</v>
@@ -12043,27 +12091,27 @@
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="1" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>6</v>
@@ -12071,13 +12119,13 @@
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>6</v>
@@ -12085,13 +12133,13 @@
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>6</v>
@@ -12099,13 +12147,13 @@
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>6</v>
@@ -12113,13 +12161,13 @@
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>6</v>
@@ -12153,38 +12201,38 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>6</v>
@@ -12192,13 +12240,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>6</v>
@@ -12206,13 +12254,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>6</v>
@@ -12220,13 +12268,13 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>6</v>
@@ -12234,27 +12282,27 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>6</v>
@@ -12262,13 +12310,13 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>6</v>
@@ -12276,13 +12324,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>6</v>
@@ -12290,13 +12338,13 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>6</v>
@@ -12304,13 +12352,13 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>6</v>
@@ -12318,27 +12366,27 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>6</v>
@@ -12346,13 +12394,13 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>6</v>
@@ -12360,13 +12408,13 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>6</v>
@@ -12374,13 +12422,13 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>6</v>
@@ -12388,13 +12436,13 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>6</v>
@@ -12402,24 +12450,27 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>1429</v>
+        <v>1430</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>6</v>
@@ -12427,13 +12478,13 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>6</v>
@@ -12441,13 +12492,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>6</v>
@@ -12455,13 +12506,13 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>6</v>
@@ -12469,13 +12520,13 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>6</v>
@@ -12483,27 +12534,27 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>6</v>
@@ -12511,13 +12562,13 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>6</v>
@@ -12525,13 +12576,13 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>6</v>
@@ -12539,13 +12590,13 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>6</v>
@@ -12553,13 +12604,13 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>6</v>
@@ -12567,27 +12618,27 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>6</v>
@@ -12595,13 +12646,13 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>6</v>
@@ -12609,13 +12660,13 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>6</v>
@@ -12623,13 +12674,13 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>6</v>
@@ -12637,13 +12688,13 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>6</v>
@@ -12651,24 +12702,27 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>1483</v>
+        <v>1484</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>6</v>
@@ -12676,13 +12730,13 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>6</v>
@@ -12690,13 +12744,13 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>6</v>
@@ -12704,13 +12758,13 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>6</v>
@@ -12718,13 +12772,13 @@
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>6</v>
@@ -12732,27 +12786,27 @@
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>6</v>
@@ -12760,13 +12814,13 @@
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>6</v>
@@ -12774,13 +12828,13 @@
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>6</v>
@@ -12788,13 +12842,13 @@
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>6</v>
@@ -12802,13 +12856,13 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>6</v>
@@ -12816,27 +12870,27 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>6</v>
@@ -12844,13 +12898,13 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>6</v>
@@ -12858,13 +12912,13 @@
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>6</v>
@@ -12872,13 +12926,13 @@
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>6</v>
@@ -12886,13 +12940,13 @@
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>6</v>
@@ -12900,24 +12954,27 @@
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>1537</v>
+        <v>1538</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>6</v>
@@ -12925,13 +12982,13 @@
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>6</v>
@@ -12939,13 +12996,13 @@
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>6</v>
@@ -12953,13 +13010,13 @@
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>6</v>
@@ -12967,13 +13024,13 @@
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>6</v>
@@ -12981,27 +13038,27 @@
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>6</v>
@@ -13009,13 +13066,13 @@
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>6</v>
@@ -13023,13 +13080,13 @@
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>6</v>
@@ -13037,13 +13094,13 @@
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>6</v>
@@ -13051,13 +13108,13 @@
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>6</v>
@@ -13065,27 +13122,27 @@
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>6</v>
@@ -13093,13 +13150,13 @@
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>6</v>
@@ -13107,13 +13164,13 @@
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>6</v>
@@ -13121,13 +13178,13 @@
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>6</v>
@@ -13135,13 +13192,13 @@
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>6</v>
@@ -13149,24 +13206,27 @@
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>1591</v>
+        <v>1592</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>6</v>
@@ -13174,13 +13234,13 @@
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>6</v>
@@ -13188,13 +13248,13 @@
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>6</v>
@@ -13202,13 +13262,13 @@
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>6</v>
@@ -13216,13 +13276,13 @@
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>6</v>
@@ -13230,27 +13290,27 @@
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>6</v>
@@ -13258,13 +13318,13 @@
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>6</v>
@@ -13272,13 +13332,13 @@
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>6</v>
@@ -13286,13 +13346,13 @@
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>6</v>
@@ -13300,13 +13360,13 @@
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>6</v>
@@ -13314,27 +13374,27 @@
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>6</v>
@@ -13342,13 +13402,13 @@
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>6</v>
@@ -13356,13 +13416,13 @@
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>6</v>
@@ -13370,13 +13430,13 @@
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>6</v>
@@ -13384,13 +13444,13 @@
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>6</v>
@@ -13398,24 +13458,27 @@
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>1645</v>
+        <v>1646</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>6</v>
@@ -13423,13 +13486,13 @@
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>6</v>
@@ -13437,13 +13500,13 @@
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>6</v>
@@ -13451,13 +13514,13 @@
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>6</v>
@@ -13465,13 +13528,13 @@
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>6</v>
@@ -13479,27 +13542,27 @@
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>6</v>
@@ -13507,13 +13570,13 @@
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>6</v>
@@ -13521,13 +13584,13 @@
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>6</v>
@@ -13535,13 +13598,13 @@
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>6</v>
@@ -13549,13 +13612,13 @@
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>6</v>
@@ -13563,27 +13626,27 @@
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>6</v>
@@ -13591,13 +13654,13 @@
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>6</v>
@@ -13605,13 +13668,13 @@
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>6</v>
@@ -13619,13 +13682,13 @@
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>6</v>
@@ -13633,13 +13696,13 @@
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>6</v>
@@ -13647,24 +13710,27 @@
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>1699</v>
+        <v>1700</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>6</v>
@@ -13672,13 +13738,13 @@
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>6</v>
@@ -13686,13 +13752,13 @@
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>6</v>
@@ -13700,13 +13766,13 @@
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>6</v>
@@ -13714,13 +13780,13 @@
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>6</v>
@@ -13728,27 +13794,27 @@
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>6</v>
+        <v>902</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>6</v>
@@ -13756,13 +13822,13 @@
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>6</v>
@@ -13770,13 +13836,13 @@
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>6</v>
@@ -13784,13 +13850,13 @@
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>6</v>
@@ -13798,13 +13864,13 @@
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>6</v>
@@ -13830,14 +13896,14 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="37.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="41.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="41.08"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
@@ -13845,10 +13911,10 @@
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -13856,10 +13922,10 @@
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -13867,10 +13933,10 @@
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -13878,10 +13944,10 @@
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -13889,10 +13955,10 @@
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -13900,10 +13966,10 @@
       <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -13911,10 +13977,10 @@
       <c r="A8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -13922,10 +13988,10 @@
       <c r="A9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -13933,10 +13999,10 @@
       <c r="A10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -13944,10 +14010,10 @@
       <c r="A11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -13955,10 +14021,10 @@
       <c r="A12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -13966,7 +14032,7 @@
       <c r="A13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="2" t="s">
         <v>38</v>
       </c>
     </row>
@@ -13974,10 +14040,10 @@
       <c r="A14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -13985,10 +14051,10 @@
       <c r="A15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -13996,10 +14062,10 @@
       <c r="A16" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14007,10 +14073,10 @@
       <c r="A17" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="F17" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14018,10 +14084,10 @@
       <c r="A18" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14029,10 +14095,10 @@
       <c r="A19" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F19" s="0" t="s">
+      <c r="F19" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14040,10 +14106,10 @@
       <c r="A20" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14051,10 +14117,10 @@
       <c r="A21" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="F21" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14062,10 +14128,10 @@
       <c r="A22" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="F22" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14073,10 +14139,10 @@
       <c r="A23" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="F23" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14084,10 +14150,10 @@
       <c r="A24" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14095,10 +14161,10 @@
       <c r="A25" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F25" s="0" t="s">
+      <c r="F25" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14106,10 +14172,10 @@
       <c r="A26" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F26" s="0" t="s">
+      <c r="F26" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14117,10 +14183,10 @@
       <c r="A27" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F27" s="0" t="s">
+      <c r="F27" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14128,10 +14194,10 @@
       <c r="A28" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F28" s="0" t="s">
+      <c r="F28" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14139,10 +14205,10 @@
       <c r="A29" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F29" s="0" t="s">
+      <c r="F29" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14150,10 +14216,10 @@
       <c r="A30" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="F30" s="0" t="s">
+      <c r="F30" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14161,7 +14227,7 @@
       <c r="A31" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="2" t="s">
         <v>92</v>
       </c>
     </row>
@@ -14169,10 +14235,10 @@
       <c r="A32" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F32" s="0" t="s">
+      <c r="F32" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14180,10 +14246,10 @@
       <c r="A33" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F33" s="0" t="s">
+      <c r="F33" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14191,10 +14257,10 @@
       <c r="A34" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F34" s="0" t="s">
+      <c r="F34" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14202,10 +14268,10 @@
       <c r="A35" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F35" s="0" t="s">
+      <c r="F35" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14213,10 +14279,10 @@
       <c r="A36" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="F36" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14224,10 +14290,10 @@
       <c r="A37" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="F37" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14235,10 +14301,10 @@
       <c r="A38" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F38" s="0" t="s">
+      <c r="F38" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14246,10 +14312,10 @@
       <c r="A39" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F39" s="0" t="s">
+      <c r="F39" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14257,10 +14323,10 @@
       <c r="A40" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="F40" s="2" t="s">
         <v>6</v>
       </c>
     </row>
